--- a/artfynd/A 42708-2022 artfynd.xlsx
+++ b/artfynd/A 42708-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42708-2022 artfynd.xlsx
+++ b/artfynd/A 42708-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16646431</v>
+        <v>57945864</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Farhällsberget S, Vstm</t>
+          <t>Lisjö, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559555.4621379424</v>
+        <v>559424</v>
       </c>
       <c r="R2" t="n">
-        <v>6617020.881302172</v>
+        <v>6617442</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
+          <t>2016-04-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
+          <t>2016-04-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,53 +777,43 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Ung gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tom Sävström, Einar Marklund, Maj Karsten</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98987383</v>
+        <v>106536719</v>
       </c>
       <c r="B3" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -843,17 +836,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lisjö, Furnäs, Vstm</t>
+          <t>Lisjö, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559131.0476497414</v>
+        <v>559225</v>
       </c>
       <c r="R3" t="n">
-        <v>6617467.606568935</v>
+        <v>6617414</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,37 +912,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106536719</v>
+        <v>56740736</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,23 +949,22 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lisjö, Vstm</t>
+          <t>Furnäs, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559225.4793170657</v>
+        <v>559472</v>
       </c>
       <c r="R4" t="n">
-        <v>6617413.558312423</v>
+        <v>6616886</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +988,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2016-01-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2016-01-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,15 +1018,578 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>63949722</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Furnäs, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559297</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6617140</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-02-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-02-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Inger-Marie Carlsen</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Inger-Marie Carlsen</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98817317</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lisjöängar, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559274</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6617666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-02-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-02-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98987383</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lisjö, Furnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559131</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6617468</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-03-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-03-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4949764</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Furnäs, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559610</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6616931</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2011-04-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2011-04-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16646431</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Farhällsberget S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>559555</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6617021</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-10-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Ung gallrad blandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Einar Marklund, Maj Karsten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42708-2022 artfynd.xlsx
+++ b/artfynd/A 42708-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57945864</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106536719</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56740736</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63949722</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98817317</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98987383</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4949764</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,8 +1630,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16646431</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>